--- a/event_planner_forms/004_fan_club_event_appearance_request_form--event_planner_forms.xlsx
+++ b/event_planner_forms/004_fan_club_event_appearance_request_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Event Planner Forms 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Event Planner Forms 7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Event Planner Forms 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_planner_forms</t>
+          <t>event_planner_forms_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -756,7 +756,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -781,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>event_planner_forms_choices</t>
+          <t>event_planner_forms_4_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>event_planner_forms_choices</t>
+          <t>event_planner_forms_4_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_planner_forms_choices</t>
+          <t>event_planner_forms_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_planner_forms_choices</t>
+          <t>event_planner_forms_5_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_planner_forms_choices</t>
+          <t>event_planner_forms_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_planner_forms_choices</t>
+          <t>event_planner_forms_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
